--- a/data/trans_orig/P21D_3_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P21D_3_R-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitando medicamentos, no los pudo comprar por motivos económicos en 2023</t>
+          <t>Población que, necesitando medicamentos, no los pudo comprar por motivos económicos en 2023 (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,97 +730,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4544</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,23%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2861</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>2,04%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3690</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>199405</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>203949</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>137485</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>140346</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>340604</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>344294</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1073,97 +1073,97 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2689</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>2439</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>0,84%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>2545</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>202033</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>204722</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>288680</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>291119</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>493296</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>495841</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1416,97 +1416,97 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>767</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1854</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3874</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>1,5%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>767</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4158</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>3368</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>1,61%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>767</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>3852</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,71%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>213632</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>215486</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>253531</t>
+          <t>253815</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>469323</t>
+          <t>469807</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4279</t>
+          <t>4392</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,47 +1794,47 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>764</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>1163</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>764</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4331</t>
+          <t>4305</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1872,7 +1872,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>522279</t>
+          <t>522166</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>319857</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>321020</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>843247</t>
+          <t>843273</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -2102,97 +2102,97 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1641</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>2966</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>687</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>3789</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>3452</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,15%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>1,67%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>687</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>3206</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>236863</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>238504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>223537</t>
+          <t>224360</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>462624</t>
+          <t>462378</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2445,97 +2445,97 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>1235</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>949</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>1063</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>155119</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>156354</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>184911</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>185860</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>341150</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>342213</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2788,97 +2788,97 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>560</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>1175</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>3232</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>0,99%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>1,89%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="R22" s="2" t="inlineStr">
         <is>
           <t>560</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="S22" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>2821</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>3102</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>1,65%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>560</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>2390</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>117031</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>118206</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>167794</t>
+          <t>167383</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>286432</t>
+          <t>285720</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3136,7 +3136,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4574</t>
+          <t>4438</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>558</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5175</t>
+          <t>5563</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>744</t>
+          <t>614</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>7418</t>
+          <t>6434</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,2%</t>
         </is>
       </c>
     </row>
@@ -3244,7 +3244,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1659204</t>
+          <t>1659340</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1588799</t>
+          <t>1588411</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1593453</t>
+          <t>1593416</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3250334</t>
+          <t>3251318</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3257008</t>
+          <t>3257138</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,8%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">

--- a/data/trans_orig/P21D_3_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P21D_3_R-Edad-trans_orig.xlsx
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>203949</t>
+          <t>210781</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>140346</t>
+          <t>162985</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>344294</t>
+          <t>373766</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>203949</t>
+          <t>210781</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>203949</t>
+          <t>210781</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>203949</t>
+          <t>210781</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>140346</t>
+          <t>162985</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>140346</t>
+          <t>162985</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>140346</t>
+          <t>162985</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>344294</t>
+          <t>373766</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>344294</t>
+          <t>373766</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>344294</t>
+          <t>373766</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>204722</t>
+          <t>226813</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>291119</t>
+          <t>250354</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>495841</t>
+          <t>477166</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>204722</t>
+          <t>226813</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>204722</t>
+          <t>226813</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>204722</t>
+          <t>226813</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>291119</t>
+          <t>250354</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>291119</t>
+          <t>250354</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>291119</t>
+          <t>250354</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>495841</t>
+          <t>477166</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>495841</t>
+          <t>477166</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>495841</t>
+          <t>477166</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>749</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1456,12 +1456,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3874</t>
+          <t>3735</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>749</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -1491,12 +1491,12 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3368</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,68%</t>
         </is>
       </c>
     </row>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>215486</t>
+          <t>252518</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1559,27 +1559,27 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>256922</t>
+          <t>295886</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>253815</t>
+          <t>292900</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>257689</t>
+          <t>296635</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1594,27 +1594,27 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>472408</t>
+          <t>548404</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>469807</t>
+          <t>545439</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>473175</t>
+          <t>549153</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,86%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>215486</t>
+          <t>252518</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>215486</t>
+          <t>252518</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>215486</t>
+          <t>252518</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>257689</t>
+          <t>296635</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>257689</t>
+          <t>296635</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>257689</t>
+          <t>296635</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>473175</t>
+          <t>549153</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>473175</t>
+          <t>549153</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>473175</t>
+          <t>549153</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>747</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1764,12 +1764,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4392</t>
+          <t>3559</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>747</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
@@ -1834,12 +1834,12 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4305</t>
+          <t>3739</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,56%</t>
         </is>
       </c>
     </row>
@@ -1867,27 +1867,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>525794</t>
+          <t>316321</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>522166</t>
+          <t>313509</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>526558</t>
+          <t>317068</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,76%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>321020</t>
+          <t>346458</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1937,27 +1937,27 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>846814</t>
+          <t>662779</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>843273</t>
+          <t>659787</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>847578</t>
+          <t>663526</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>99,91%</t>
+          <t>99,89%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>526558</t>
+          <t>317068</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>526558</t>
+          <t>317068</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>526558</t>
+          <t>317068</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>321020</t>
+          <t>346458</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>321020</t>
+          <t>346458</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>321020</t>
+          <t>346458</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>847578</t>
+          <t>663526</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>847578</t>
+          <t>663526</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>847578</t>
+          <t>663526</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>702</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2966</t>
+          <t>3505</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,7 +2167,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>702</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -2177,12 +2177,12 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3452</t>
+          <t>3546</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,69%</t>
         </is>
       </c>
     </row>
@@ -2210,7 +2210,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>238504</t>
+          <t>257481</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2245,27 +2245,27 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>226639</t>
+          <t>253474</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>224360</t>
+          <t>250671</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>227326</t>
+          <t>254176</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2280,27 +2280,27 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>465143</t>
+          <t>510955</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>462378</t>
+          <t>508111</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>465830</t>
+          <t>511657</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,86%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>238504</t>
+          <t>257481</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>238504</t>
+          <t>257481</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>238504</t>
+          <t>257481</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>227326</t>
+          <t>254176</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>227326</t>
+          <t>254176</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>227326</t>
+          <t>254176</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>465830</t>
+          <t>511657</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>465830</t>
+          <t>511657</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>465830</t>
+          <t>511657</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2553,7 +2553,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>156354</t>
+          <t>174053</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>185860</t>
+          <t>199573</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>342213</t>
+          <t>373626</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>156354</t>
+          <t>174053</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>156354</t>
+          <t>174053</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>156354</t>
+          <t>174053</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>185860</t>
+          <t>199573</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>185860</t>
+          <t>199573</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>185860</t>
+          <t>199573</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>342213</t>
+          <t>373626</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>342213</t>
+          <t>373626</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>342213</t>
+          <t>373626</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>561</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3232</t>
+          <t>2831</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>561</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3102</t>
+          <t>2803</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>0,89%</t>
         </is>
       </c>
     </row>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>118206</t>
+          <t>129561</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2931,27 +2931,27 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>170055</t>
+          <t>186194</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>167383</t>
+          <t>183924</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>170615</t>
+          <t>186755</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2966,27 +2966,27 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>288262</t>
+          <t>315755</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>285720</t>
+          <t>313513</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>288822</t>
+          <t>316316</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,82%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>118206</t>
+          <t>129561</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>118206</t>
+          <t>129561</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>118206</t>
+          <t>129561</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>170615</t>
+          <t>186755</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>170615</t>
+          <t>186755</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>170615</t>
+          <t>186755</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>288822</t>
+          <t>316316</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>288822</t>
+          <t>316316</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>288822</t>
+          <t>316316</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,7 +3126,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>747</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -3136,7 +3136,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4438</t>
+          <t>4551</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3166,17 +3166,17 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>564</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5563</t>
+          <t>5521</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,22 +3196,22 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>2778</t>
+          <t>2759</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>705</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6434</t>
+          <t>6677</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
@@ -3239,17 +3239,17 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1663014</t>
+          <t>1567527</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1659340</t>
+          <t>1563723</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1663778</t>
+          <t>1568274</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,7 +3259,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3274,27 +3274,27 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1591961</t>
+          <t>1694923</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1588411</t>
+          <t>1691415</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1593416</t>
+          <t>1696372</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>99,88%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3309,22 +3309,22 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>3254974</t>
+          <t>3262451</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3251318</t>
+          <t>3258533</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3257138</t>
+          <t>3264505</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>99,91%</t>
+          <t>99,92%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1663778</t>
+          <t>1568274</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1663778</t>
+          <t>1568274</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1663778</t>
+          <t>1568274</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1593974</t>
+          <t>1696936</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1593974</t>
+          <t>1696936</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1593974</t>
+          <t>1696936</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>3257752</t>
+          <t>3265210</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>3257752</t>
+          <t>3265210</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>3257752</t>
+          <t>3265210</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
